--- a/template.xlsx
+++ b/template.xlsx
@@ -1,26 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\longh\Dropbox\DOE\Semi-para-bayes-shinylive\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\longh\Dropbox\claude\myapp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D31DEA3B-B360-47FA-8BE2-3BA9C2CF5989}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63E368E5-350A-42FB-B3EF-2F6380F654A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{8C91F151-A49C-4E44-AE7C-4F3BE0E59E1A}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Definition" sheetId="1" r:id="rId1"/>
     <sheet name="Data" sheetId="2" r:id="rId2"/>
+    <sheet name="Constraints" sheetId="3" r:id="rId3"/>
+    <sheet name="Model" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -35,53 +34,51 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="43">
+  <si>
+    <t>Parameter</t>
+  </si>
+  <si>
+    <t>Min</t>
+  </si>
+  <si>
+    <t>Standard</t>
+  </si>
+  <si>
+    <t>Max</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Interval</t>
+  </si>
+  <si>
+    <t>Purpose</t>
+  </si>
   <si>
     <t>X1</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Parameter</t>
-    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>continuous</t>
+  </si>
+  <si>
+    <t>X2</t>
+  </si>
+  <si>
+    <t>X3</t>
+  </si>
+  <si>
+    <t>categorical</t>
   </si>
   <si>
     <t>Y1</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Purpose</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>X2</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>continuous</t>
-  </si>
-  <si>
-    <t>Type</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Max</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Standard</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Min</t>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>id</t>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>id1</t>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>id2</t>
@@ -96,60 +93,139 @@
     <t>id5</t>
   </si>
   <si>
+    <t>rbf</t>
+  </si>
+  <si>
+    <t>theta2</t>
+  </si>
+  <si>
+    <t>sigma2</t>
+  </si>
+  <si>
+    <t>prior</t>
+  </si>
+  <si>
+    <t>(intercept)_mu</t>
+  </si>
+  <si>
+    <t>X1_mu</t>
+  </si>
+  <si>
+    <t>X2_mu</t>
+  </si>
+  <si>
+    <t>(intercept)_var</t>
+  </si>
+  <si>
+    <t>X1_var</t>
+  </si>
+  <si>
+    <t>X2_var</t>
+  </si>
+  <si>
+    <t>Y2</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>&lt;2</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>One expression per row (delete the examples above and add your own). Ex) X1 + X2 &lt; 4</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Use variable names exactly as in Definition (X1, X2, ...). X1 * X2 &gt;= 0.5</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Operators: &lt;  &lt;=  &gt;  &gt;=   |   Blank rows are ignored. X2 - X1 &lt;= 1</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Target Y</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Y1</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>=5</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
     <t>X3</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>&gt;5</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Interval</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>categorical</t>
-  </si>
-  <si>
-    <t>A</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>B</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>C</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Expression</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Note</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>type</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>parameter</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>value</t>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="6"/>
-      <name val="游ゴシック"/>
-      <family val="2"/>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
       <charset val="128"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E78"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -162,20 +238,27 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-  </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -188,9 +271,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -198,44 +281,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -263,31 +346,14 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -315,26 +381,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -343,181 +392,204 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F48270D-72D4-48A5-A707-03F76BD008F5}">
-  <dimension ref="A1:G5"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="5" max="5" width="10.58203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.58203125" customWidth="1"/>
-    <col min="7" max="7" width="16.08203125" customWidth="1"/>
+    <col min="1" max="1" width="11.90625" customWidth="1"/>
+    <col min="5" max="5" width="16.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D1" t="s">
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>7</v>
-      </c>
-      <c r="E1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" t="s">
-        <v>0</v>
       </c>
       <c r="B2">
         <v>-2</v>
@@ -529,15 +601,16 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F2">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" ht="15.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="G2" s="2"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -549,51 +622,64 @@
         <v>2</v>
       </c>
       <c r="E3" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F3">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" ht="15.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="G3" s="2"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" t="s">
-        <v>22</v>
+        <v>10</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>2</v>
       </c>
       <c r="E4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+        <v>11</v>
+      </c>
+      <c r="G4" s="2"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5">
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E5" t="s">
-        <v>5</v>
-      </c>
-      <c r="G5" t="s">
-        <v>17</v>
+        <v>8</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1"/>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E5" xr:uid="{CEF468C1-A95A-423E-91B3-90515CCFC354}">
+  <phoneticPr fontId="2"/>
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E6" xr:uid="{CF0CD112-72CA-4371-9E45-9F6233AF51E9}">
       <formula1>"continuous, categorical"</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F6" xr:uid="{B3A7734C-B550-4D7D-8DB3-D9282F132E24}">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:D6" xr:uid="{BF3F67E7-5699-4E80-95F9-19367A628CB0}">
+      <formula1>B2</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -601,30 +687,30 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5452353B-CFEB-4038-9563-2FA49DB2F36C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B2">
         <v>-1</v>
@@ -632,16 +718,16 @@
       <c r="C2">
         <v>1</v>
       </c>
-      <c r="D2" t="s">
-        <v>21</v>
+      <c r="D2">
+        <v>1</v>
       </c>
       <c r="E2">
         <v>-3.0858960999999998</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B3">
         <v>-0.5</v>
@@ -649,16 +735,16 @@
       <c r="C3">
         <v>1</v>
       </c>
-      <c r="D3" t="s">
-        <v>21</v>
+      <c r="D3">
+        <v>1</v>
       </c>
       <c r="E3">
         <v>-0.88129469999999999</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -666,16 +752,16 @@
       <c r="C4">
         <v>1</v>
       </c>
-      <c r="D4" t="s">
-        <v>21</v>
+      <c r="D4">
+        <v>1</v>
       </c>
       <c r="E4">
         <v>-0.71955829999999998</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B5">
         <v>0.5</v>
@@ -683,16 +769,16 @@
       <c r="C5">
         <v>1</v>
       </c>
-      <c r="D5" t="s">
-        <v>20</v>
+      <c r="D5">
+        <v>0</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -700,15 +786,198 @@
       <c r="C6">
         <v>1</v>
       </c>
-      <c r="D6" t="s">
-        <v>22</v>
+      <c r="D6">
+        <v>2</v>
       </c>
       <c r="E6">
         <v>0.51127409999999995</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1"/>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="86.1796875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="3" max="3" width="19.1796875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2"/>
+  <dataValidations count="1">
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D3 D7:D9" xr:uid="{9DAA9B2D-375A-4DB3-8CD7-E0E6B4991FC1}">
+      <formula1>0</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>